--- a/dataset_t6_grouped/results2/G5/G5_T6588_W0053F0003T0006Z000C1N63_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6588_W0053F0003T0006Z000C1N63_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>5.310861067248092</v>
+        <v>0.8630149234278149</v>
       </c>
       <c r="D2" t="n">
-        <v>2.205318306343976</v>
+        <v>0.3583642247808961</v>
       </c>
       <c r="E2" t="n">
-        <v>2.487015699535097</v>
+        <v>0.4041400511744533</v>
       </c>
       <c r="F2" t="n">
-        <v>2.476251066695444</v>
+        <v>0.4023907983380097</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>10.28489246631829</v>
+        <v>1.671295025776722</v>
       </c>
       <c r="D3" t="n">
-        <v>7.157820439734864</v>
+        <v>1.163145821456915</v>
       </c>
       <c r="E3" t="n">
-        <v>2.487015699535097</v>
+        <v>0.4041400511744533</v>
       </c>
       <c r="F3" t="n">
-        <v>2.476251066695444</v>
+        <v>0.4023907983380097</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
